--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488219_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488219_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1729</v>
+        <v>3.9468</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8735</v>
+        <v>0.9921</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2994</v>
+        <v>2.9547</v>
       </c>
       <c r="G2" t="n">
         <v>0.4074</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7661</v>
+        <v>0.54</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1379</v>
+        <v>0.2565</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6282</v>
+        <v>0.2835</v>
       </c>
       <c r="V2" t="n">
         <v>1.8877</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3481</v>
+        <v>3.4707</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8274</v>
+        <v>1.9253</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5208</v>
+        <v>1.5454</v>
       </c>
       <c r="G3" t="n">
         <v>4.46</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0383</v>
+        <v>0.0843</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2226</v>
+        <v>-0.1246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1843</v>
+        <v>0.2089</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2589</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5589</v>
+        <v>2.4095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8153</v>
+        <v>1.1091</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7436</v>
+        <v>1.3004</v>
       </c>
       <c r="G4" t="n">
         <v>0.4755</v>
@@ -766,13 +766,13 @@
         <v>3.5205</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9717</v>
+        <v>0.8223</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2661</v>
+        <v>0.5599</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7056</v>
+        <v>0.2624</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7361</v>
+        <v>1.8575</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2824</v>
+        <v>0.0114</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0184</v>
+        <v>1.8461</v>
       </c>
       <c r="G5" t="n">
         <v>1.4321</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3636</v>
+        <v>-0.2422</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8207</v>
+        <v>-0.5269</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4571</v>
+        <v>0.2848</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6294</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6415</v>
+        <v>1.7657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9899</v>
+        <v>0.7941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6515</v>
+        <v>0.9716</v>
       </c>
       <c r="G6" t="n">
         <v>1.1191</v>
@@ -922,13 +922,13 @@
         <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.422</v>
+        <v>-0.2978</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1131</v>
+        <v>-0.309</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3089</v>
+        <v>0.0112</v>
       </c>
       <c r="V6" t="n">
         <v>0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5458</v>
+        <v>0.6683</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2227</v>
+        <v>0.3207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.323</v>
+        <v>0.3477</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4058</v>
@@ -1078,13 +1078,13 @@
         <v>2.9646</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2104</v>
+        <v>0.333</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4303</v>
+        <v>0.5282</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2199</v>
+        <v>-0.1952</v>
       </c>
       <c r="V8" t="n">
         <v>1.2589</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8123</v>
+        <v>-0.8565</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8168</v>
+        <v>-0.0334</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5989</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5104</v>
+        <v>-0.5546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9849</v>
+        <v>-0.2014</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5255</v>
+        <v>-0.3532</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>H. GREVELS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9842</v>
+        <v>-1.9854</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0539</v>
+        <v>-1.329</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9302</v>
+        <v>-0.6564</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1173</v>
+        <v>-1.6458</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7303</v>
+        <v>-0.6012</v>
       </c>
       <c r="I10" t="n">
-        <v>0.613</v>
+        <v>-1.0446</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5889</v>
+        <v>-1.2628</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1161</v>
+        <v>0.0429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.705</v>
+        <v>-1.3057</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7063</v>
+        <v>-0.383</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6143</v>
+        <v>-0.6441</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.092</v>
+        <v>0.2611</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.671</v>
+        <v>-0.0252</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1926</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5215</v>
+        <v>0.041</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9444</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. GREVELS</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1079</v>
+        <v>-2.3604</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4269</v>
+        <v>-1.1225</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.681</v>
+        <v>-1.2378</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6458</v>
+        <v>-2.5477</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6012</v>
+        <v>-1.5709</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0446</v>
+        <v>-0.9768</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2628</v>
+        <v>0.6574</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0429</v>
+        <v>1.2581</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3057</v>
+        <v>-0.6007</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.383</v>
+        <v>-3.2051</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6441</v>
+        <v>-2.829</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2611</v>
+        <v>-0.3761</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1477</v>
+        <v>0.0762</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1641</v>
+        <v>0.3324</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0164</v>
+        <v>-0.2562</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3363</v>
+        <v>-2.4727</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0246</v>
+        <v>-1.7394</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3117</v>
+        <v>-0.7333</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5477</v>
+        <v>-2.1173</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5709</v>
+        <v>-2.7303</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9768</v>
+        <v>0.613</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6574</v>
+        <v>0.5889</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2581</v>
+        <v>-0.1161</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6007</v>
+        <v>0.705</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2051</v>
+        <v>-2.7063</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.829</v>
+        <v>-2.6143</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3761</v>
+        <v>-0.092</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7411</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.4823</v>
+        <v>-3.1499</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1002</v>
+        <v>0.1825</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4303</v>
+        <v>0.5071</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.33</v>
+        <v>-0.3246</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.63</v>
+        <v>0.9444</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.0067</v>
+        <v>7.6876</v>
       </c>
       <c r="E13" t="n">
-        <v>2.368299999999999</v>
+        <v>2.172499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.638299999999999</v>
+        <v>5.5153</v>
       </c>
       <c r="G13" t="n">
         <v>-1.177299999999999</v>
@@ -1441,7 +1441,7 @@
         <v>10.2084</v>
       </c>
       <c r="J13" t="n">
-        <v>9.9115</v>
+        <v>9.911500000000002</v>
       </c>
       <c r="K13" t="n">
         <v>4.389399999999999</v>
@@ -1459,7 +1459,7 @@
         <v>4.6865</v>
       </c>
       <c r="P13" t="n">
-        <v>5.743799999999999</v>
+        <v>5.7438</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7848</v>
@@ -1468,13 +1468,13 @@
         <v>18.5287</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2374</v>
+        <v>0.9185000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1518</v>
+        <v>0.956</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0858000000000001</v>
+        <v>-0.03739999999999988</v>
       </c>
       <c r="V13" t="n">
         <v>2.2027</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.014699999999999</v>
+        <v>7.5161</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5516</v>
+        <v>5.9641</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4631</v>
+        <v>1.5521</v>
       </c>
       <c r="G14" t="n">
         <v>8.639900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>2.594</v>
       </c>
       <c r="S14" t="n">
-        <v>2.116</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8643</v>
+        <v>0.2767</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2517</v>
+        <v>0.3407</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6294</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3423</v>
+        <v>2.7821</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9388</v>
+        <v>3.8616</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5965</v>
+        <v>-1.0795</v>
       </c>
       <c r="G15" t="n">
         <v>1.662</v>
@@ -1624,13 +1624,13 @@
         <v>2.2234</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3833</v>
+        <v>-0.1769</v>
       </c>
       <c r="T15" t="n">
-        <v>1.736</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3527</v>
+        <v>-0.8357</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7696</v>
+        <v>1.5883</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8801</v>
+        <v>1.5883</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8895</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5573</v>
+        <v>1.5883</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9659</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4086</v>
+        <v>0.6221</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0291</v>
+        <v>1.5883</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8004</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.7713</v>
+        <v>0.6221</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4718</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1655</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6373</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2226</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.008200000000000001</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5883</v>
+        <v>1.4741</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5883</v>
+        <v>0.8801</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5883</v>
+        <v>1.5573</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9661999999999999</v>
+        <v>3.9659</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6221</v>
+        <v>-2.4086</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5883</v>
+        <v>2.0291</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9661999999999999</v>
+        <v>3.8004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6221</v>
+        <v>-1.7713</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.4718</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.1655</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.6373</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.5099</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.2226</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.2873</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3966</v>
+        <v>0.3474</v>
       </c>
       <c r="E20" t="n">
         <v>0.3241</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0725</v>
+        <v>0.0232</v>
       </c>
       <c r="G20" t="n">
         <v>0.0267</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0555</v>
+        <v>0.0062</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1102</v>
+        <v>0.0609</v>
       </c>
       <c r="V20" t="n">
         <v>0.3144</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>J. CANDELA SOLO DE ZALDIVAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6832</v>
+        <v>-0.5881</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1729</v>
+        <v>0.1291</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5102</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5475</v>
+        <v>-0.036</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.408</v>
+        <v>-0.5583</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9555</v>
+        <v>0.5223</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1365</v>
+        <v>0.0859</v>
       </c>
       <c r="K22" t="n">
-        <v>1.095</v>
+        <v>0.0859</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.589</v>
+        <v>-0.1219</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.503</v>
+        <v>-0.6441</v>
       </c>
       <c r="O22" t="n">
-        <v>0.914</v>
+        <v>0.5223</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3808</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5434</v>
+        <v>0.0432</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1627</v>
+        <v>0.0336</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CANDELA SOLO DE ZALDIVAR</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7845</v>
+        <v>-0.9271</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0312</v>
+        <v>-0.5646</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8156</v>
+        <v>-0.3625</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.036</v>
+        <v>0.5475</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5583</v>
+        <v>-0.408</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5223</v>
+        <v>0.9555</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0859</v>
+        <v>1.1365</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0859</v>
+        <v>1.095</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1219</v>
+        <v>-0.589</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6441</v>
+        <v>-1.503</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5223</v>
+        <v>0.914</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1196</v>
+        <v>0.1368</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0547</v>
+        <v>0.1517</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0649</v>
+        <v>-0.0149</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9649</v>
+        <v>-1.9156</v>
       </c>
       <c r="E24" t="n">
         <v>-1.1453</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8196</v>
+        <v>-0.7704</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8524</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.186</v>
+        <v>-0.1368</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8138</v>
+        <v>-2.7097</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1176</v>
+        <v>-3.4321</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3038</v>
+        <v>0.7224</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3691</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5738</v>
+        <v>-0.4698</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8207</v>
+        <v>-0.1352</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7531</v>
+        <v>-0.3345</v>
       </c>
       <c r="V25" t="n">
         <v>0.3144</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6951</v>
+        <v>-3.7892</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8481</v>
+        <v>-2.9667</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8471</v>
+        <v>-0.8224</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9571</v>
@@ -2482,13 +2482,13 @@
         <v>2.4087</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.441</v>
+        <v>-0.535</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2584</v>
+        <v>-0.3771</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1826</v>
+        <v>-0.158</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.5816</v>
+        <v>-6.5575</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.7815</v>
+        <v>-5.6836</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8001</v>
+        <v>-0.8739</v>
       </c>
       <c r="G27" t="n">
         <v>-4.7148</v>
@@ -2560,13 +2560,13 @@
         <v>1.4823</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0602</v>
+        <v>0.0843</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.0584</v>
+        <v>0.0395</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1186</v>
+        <v>0.0448</v>
       </c>
       <c r="V27" t="n">
         <v>-0.63</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.8952</v>
+        <v>-7.5276</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.4011</v>
+        <v>-7.1073</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4942</v>
+        <v>-0.4203</v>
       </c>
       <c r="G28" t="n">
         <v>-4.7413</v>
@@ -2638,13 +2638,13 @@
         <v>0.3706</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4308</v>
+        <v>-0.0631</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4924</v>
+        <v>-0.1986</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0617</v>
+        <v>0.1355</v>
       </c>
       <c r="V28" t="n">
         <v>-0.3144</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-8.740500000000001</v>
+        <v>-8.740499999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.586100000000003</v>
+        <v>-6.586000000000002</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.1544</v>
+        <v>-2.1545</v>
       </c>
       <c r="G29" t="n">
         <v>0.9173</v>
@@ -2716,13 +2716,13 @@
         <v>12.9701</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.9698000000000007</v>
+        <v>-0.9700000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.03709999999999997</v>
+        <v>-0.03719999999999998</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.9328</v>
+        <v>-0.9328000000000001</v>
       </c>
       <c r="V29" t="n">
         <v>-2.2027</v>
